--- a/stories/arbres/TREE-SAN-013.xlsx
+++ b/stories/arbres/TREE-SAN-013.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est à l'école. Puis maman vient. Papa aussi. Après le goûter, on prend la brosse. Le matin, déjà. Le soir, encore. Un adulte est avec Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a croqué une pomme. Des petits bouts restent. Maman dit : la brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin, c'était fait. Le soir, ce sera fait.</t>
+          <t>Tom a croqué une pomme. Des petits bouts restent. La brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin, c'était fait. Le soir, ce sera fait.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a croqué une pomme. Des petits bouts restent.
+maman|La brosse.
+narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin, c'était fait. Le soir, ce sera fait.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Après la pomme, Tom prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|La pomme est finie. Tom a brossé. Le matin. Le soir. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2231,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2398,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va à la cuisine. Un verre d'eau. Il a pris la brosse. Maman, l'adulte, sourit. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2593,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2760,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom empile les cubes. Il a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2927,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3094,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom ouvre le livre. Il a pris la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3261,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3428,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom fait la dînette. Il a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3595,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3762,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va au jardin. L'air est frais. Il a brossé. Un adulte l'a aidé. Le matin. Le soir, encore.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3863,6 +3957,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4025,6 +4124,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au jardin. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4291,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4458,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sur le banc. Tom a pris la brosse. Le matin, le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4625,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4792,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette sous l'arbre. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4959,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5126,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va dans la chambre. Il a pris la brosse. Papa, l'adulte, range. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,6 +5321,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5349,6 +5488,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au tapis. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5655,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5822,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre sous la lampe. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5989,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6156,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette des peluches. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6323,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6352,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom a mangé un yaourt. La cuillère est propre. Papa dit : la brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin déjà. Le soir encore.</t>
+          <t>Tom a mangé un yaourt. La cuillère est propre. La brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin déjà. Le soir encore.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6490,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a mangé un yaourt. La cuillère est propre.
+papa|La brosse.
+narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin déjà. Le soir encore.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6673,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après le yaourt, Tom prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6846,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le yaourt est fini. Tom a brossé. Matin et soir. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7041,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7208,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la cuisine, Tom range le pot. Il a pris la brosse. Un adulte l'a aidé. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7207,6 +7403,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7369,6 +7570,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes à la cuisine. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7737,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7904,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre de recettes. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8071,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8238,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette près du buffet. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8405,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8572,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Tom court un peu. Il a brossé. Un adulte. Le matin. Le soir, la brosse reviendra.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8531,6 +8767,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8693,6 +8934,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au soleil. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9101,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9268,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sous le cerisier. Tom a pris la brosse. Le matin, le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9435,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9602,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette sur la nappe. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9769,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9936,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Tom s'étire. Il a pris la brosse. Papa, l'adulte. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9855,6 +10131,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10017,6 +10298,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Une tour de cubes. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10465,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10632,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre des animaux. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10799,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10966,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette des doudous. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11133,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11162,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom a mangé un morceau de pain. Des miettes. Maman dit : la brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin. Le soir. Pareil.</t>
+          <t>Tom a mangé un morceau de pain. Des miettes. La brosse. Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin. Le soir. Pareil.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11300,13 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a mangé un morceau de pain. Des miettes.
+maman|La brosse.
+narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin. Le soir. Pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11483,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Après le pain, Tom prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11656,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Les miettes sont parties. Tom a brossé. Matin et soir. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11851,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12018,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|À la cuisine, Tom essuie la table. Il a pris la brosse. Maman, l'adulte. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11875,6 +12213,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12037,6 +12380,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes et table propre. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12547,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12714,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sur la table. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12881,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13048,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette après le pain. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13215,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13382,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Tom cherche un caillou. Il a brossé. Un adulte. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13199,6 +13577,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13361,6 +13744,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes près des cailloux. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13911,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14078,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sur le banc. Tom a pris la brosse. Le matin, le soir, avec un adulte. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14245,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14412,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette sous le tilleul. Tom a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14579,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14746,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Tom range une chaussette. Il a pris la brosse. Papa, l'adulte. Le matin. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14523,6 +14941,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14685,6 +15108,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au pied du lit. Tom a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15275,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15442,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre sous la lampe. Tom a pris la brosse. Le matin, le soir, un adulte. Maman range.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15609,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15776,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette des doudous. Tom a la brosse. Matin et soir, avec un adulte. Ils se taisent une seconde.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15943,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15530,6 +15983,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-013.xlsx
+++ b/stories/arbres/TREE-SAN-013.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Tom est à l'école. Puis maman vient. Papa aussi. Après le goûter, on prend la brosse. Le matin, déjà. Le soir, encore. Un adulte est avec Tom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
 narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin, c'était fait. Le soir, ce sera fait.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Après la pomme, Tom prend quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|La pomme est finie. Tom a brossé. Le matin. Le soir. Un adulte.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2236,6 +2246,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2403,6 +2414,7 @@
           <t>narrateur|Tom va à la cuisine. Un verre d'eau. Il a pris la brosse. Maman, l'adulte, sourit. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2598,6 +2610,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2765,6 +2778,7 @@
           <t>narrateur|Tom empile les cubes. Il a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2932,6 +2946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3099,6 +3114,7 @@
           <t>narrateur|Tom ouvre le livre. Il a pris la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3266,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3433,6 +3450,7 @@
           <t>narrateur|Tom fait la dînette. Il a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3600,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3767,6 +3786,7 @@
           <t>narrateur|Tom va au jardin. L'air est frais. Il a brossé. Un adulte l'a aidé. Le matin. Le soir, encore.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3962,6 +3982,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4129,6 +4150,7 @@
           <t>narrateur|Cubes au jardin. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4296,6 +4318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4463,6 +4486,7 @@
           <t>narrateur|Un livre sur le banc. Tom a pris la brosse. Le matin, le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4630,6 +4654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4797,6 +4822,7 @@
           <t>narrateur|Dînette sous l'arbre. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4964,6 +4990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5131,6 +5158,7 @@
           <t>narrateur|Tom va dans la chambre. Il a pris la brosse. Papa, l'adulte, range. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5326,6 +5354,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5493,6 +5522,7 @@
           <t>narrateur|Cubes au tapis. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5660,6 +5690,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5827,6 +5858,7 @@
           <t>narrateur|Le livre sous la lampe. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5994,6 +6026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6161,6 +6194,7 @@
           <t>narrateur|La dînette des peluches. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6328,6 +6362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6497,6 +6532,7 @@
 narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin déjà. Le soir encore.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6680,6 +6716,7 @@
           <t>narrateur|Après le yaourt, Tom prend quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6851,6 +6888,7 @@
           <t>narrateur|Le yaourt est fini. Tom a brossé. Matin et soir. Un adulte.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7046,6 +7084,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7213,6 +7252,7 @@
           <t>narrateur|À la cuisine, Tom range le pot. Il a pris la brosse. Un adulte l'a aidé. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7408,6 +7448,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7575,6 +7616,7 @@
           <t>narrateur|Cubes à la cuisine. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7742,6 +7784,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7909,6 +7952,7 @@
           <t>narrateur|Un livre de recettes. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8076,6 +8120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8243,6 +8288,7 @@
           <t>narrateur|Dînette près du buffet. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8410,6 +8456,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8577,6 +8624,7 @@
           <t>narrateur|Au jardin, Tom court un peu. Il a brossé. Un adulte. Le matin. Le soir, la brosse reviendra.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8772,6 +8820,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8939,6 +8988,7 @@
           <t>narrateur|Cubes au soleil. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9106,6 +9156,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9273,6 +9324,7 @@
           <t>narrateur|Un livre sous le cerisier. Tom a pris la brosse. Le matin, le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9440,6 +9492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9607,6 +9660,7 @@
           <t>narrateur|Dînette sur la nappe. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9774,6 +9828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9941,6 +9996,7 @@
           <t>narrateur|Dans la chambre, Tom s'étire. Il a pris la brosse. Papa, l'adulte. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10136,6 +10192,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10303,6 +10360,7 @@
           <t>narrateur|Une tour de cubes. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10470,6 +10528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10637,6 +10696,7 @@
           <t>narrateur|Le livre des animaux. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10804,6 +10864,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10971,6 +11032,7 @@
           <t>narrateur|La dînette des doudous. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11138,6 +11200,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11307,6 +11370,7 @@
 narrateur|Un adulte est là. Tom prend sa brosse. Ils brossent. Le matin. Le soir. Pareil.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11490,6 +11554,7 @@
           <t>narrateur|Après le pain, Tom prend quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11661,6 +11726,7 @@
           <t>narrateur|Les miettes sont parties. Tom a brossé. Matin et soir. Un adulte.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11856,6 +11922,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12023,6 +12090,7 @@
           <t>narrateur|À la cuisine, Tom essuie la table. Il a pris la brosse. Maman, l'adulte. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12218,6 +12286,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12385,6 +12454,7 @@
           <t>narrateur|Cubes et table propre. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12552,6 +12622,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12719,6 +12790,7 @@
           <t>narrateur|Un livre sur la table. Tom a pris la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12886,6 +12958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13053,6 +13126,7 @@
           <t>narrateur|Dînette après le pain. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13220,6 +13294,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13387,6 +13462,7 @@
           <t>narrateur|Au jardin, Tom cherche un caillou. Il a brossé. Un adulte. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13582,6 +13658,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13749,6 +13826,7 @@
           <t>narrateur|Cubes près des cailloux. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13916,6 +13994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14083,6 +14162,7 @@
           <t>narrateur|Un livre sur le banc. Tom a pris la brosse. Le matin, le soir, avec un adulte. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14250,6 +14330,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14417,6 +14498,7 @@
           <t>narrateur|Dînette sous le tilleul. Tom a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14584,6 +14666,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14751,6 +14834,7 @@
           <t>narrateur|Dans la chambre, Tom range une chaussette. Il a pris la brosse. Papa, l'adulte. Le matin. Le soir.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14946,6 +15030,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15113,6 +15198,7 @@
           <t>narrateur|Cubes au pied du lit. Tom a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15280,6 +15366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15447,6 +15534,7 @@
           <t>narrateur|Le livre sous la lampe. Tom a pris la brosse. Le matin, le soir, un adulte. Maman range.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15614,6 +15702,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15781,6 +15870,7 @@
           <t>narrateur|La dînette des doudous. Tom a la brosse. Matin et soir, avec un adulte. Ils se taisent une seconde.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15948,6 +16038,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15966,7 +16057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15990,6 +16081,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16191,6 +16296,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
